--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_shipment_manifest_q1_q2_2024.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_shipment_manifest_q1_q2_2024.xlsx
@@ -612,17 +612,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VALPO-9000000001</t>
+          <t>PO 9001000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VALPART-RG213-001</t>
+          <t>QZ-3001</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -657,17 +657,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VALPO-9000000003</t>
+          <t>PO 9001000003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VALPART-FAN-006</t>
+          <t>QZ-3006</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -702,17 +702,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VALPO-9000000009</t>
+          <t>PO 9001000009</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VALPART-NIC-013</t>
+          <t>QZ-3013</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -747,17 +747,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VALPO-9000000012</t>
+          <t>PO 9001000012</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VALPART-FLT-009</t>
+          <t>QZ-3009</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -792,17 +792,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VALPO-9000000002</t>
+          <t>PO 9001000002</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -837,17 +837,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VALPO-9000000007</t>
+          <t>PO 9001000007</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VALPART-SFP-014</t>
+          <t>QZ-3014</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -882,17 +882,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VALPO-9000000004</t>
+          <t>PO 9001000004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VALPART-GPSANT-004</t>
+          <t>QZ-3004</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -927,17 +927,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VALPO-9000000011</t>
+          <t>PO 9001000011</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VALPART-BATT-007</t>
+          <t>QZ-3007</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -972,17 +972,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VALPO-9000000006</t>
+          <t>PO 9001000006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VALPART-ROUTER-016</t>
+          <t>QZ-3016</t>
         </is>
       </c>
       <c r="F10" t="n">
